--- a/Pin Connections 3.xlsb.xlsx
+++ b/Pin Connections 3.xlsb.xlsx
@@ -1,28 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stead\OneDrive\TimeJudge\Current TimeJudge code and devices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC34659C-A5C5-415D-91D6-2BBC218D8D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB7C811-16ED-427E-BCA5-32CA99E80309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controller" sheetId="1" r:id="rId1"/>
     <sheet name="Screens" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Costs" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="81">
   <si>
     <t>gnd</t>
   </si>
@@ -178,12 +189,102 @@
   </si>
   <si>
     <t>16-pin HUB08 Matrix</t>
+  </si>
+  <si>
+    <t>Teensy 3.2</t>
+  </si>
+  <si>
+    <t>Component:</t>
+  </si>
+  <si>
+    <t>€</t>
+  </si>
+  <si>
+    <t>HC12</t>
+  </si>
+  <si>
+    <t>LIPO chg</t>
+  </si>
+  <si>
+    <t>OLED</t>
+  </si>
+  <si>
+    <t>MRFC522</t>
+  </si>
+  <si>
+    <t>LiPo batts</t>
+  </si>
+  <si>
+    <t>case</t>
+  </si>
+  <si>
+    <t>aerial</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>Screen Unit</t>
+  </si>
+  <si>
+    <t>STM32</t>
+  </si>
+  <si>
+    <t>Sounder</t>
+  </si>
+  <si>
+    <t>Aerial</t>
+  </si>
+  <si>
+    <t>Case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matrix Driver </t>
+  </si>
+  <si>
+    <t>LiFePO4 batt</t>
+  </si>
+  <si>
+    <t>Connector</t>
+  </si>
+  <si>
+    <t>Charger</t>
+  </si>
+  <si>
+    <t>Charge Controller</t>
+  </si>
+  <si>
+    <t>Transistor Sw</t>
+  </si>
+  <si>
+    <t>Switch</t>
+  </si>
+  <si>
+    <t>qty</t>
+  </si>
+  <si>
+    <t>Screen Unit x2</t>
+  </si>
+  <si>
+    <t>Boost</t>
+  </si>
+  <si>
+    <t>Buck</t>
+  </si>
+  <si>
+    <t>STM32F103</t>
+  </si>
+  <si>
+    <t>Matrix Controller</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$€-2]\ #,##0.00"/>
+  </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -698,7 +799,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -890,17 +991,47 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -913,48 +1044,22 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2210,34 +2315,34 @@
     </row>
     <row r="3" spans="2:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:51" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="116" t="s">
+      <c r="B4" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="117"/>
-      <c r="L4" s="120" t="s">
+      <c r="C4" s="135"/>
+      <c r="L4" s="125" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121"/>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111"/>
-      <c r="R4" s="112"/>
-      <c r="AB4" s="109" t="s">
+      <c r="M4" s="126"/>
+      <c r="N4" s="126"/>
+      <c r="O4" s="126"/>
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="122"/>
+      <c r="AB4" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="AC4" s="110"/>
-      <c r="AD4" s="111"/>
-      <c r="AE4" s="112"/>
-      <c r="AO4" s="120" t="s">
+      <c r="AC4" s="133"/>
+      <c r="AD4" s="121"/>
+      <c r="AE4" s="122"/>
+      <c r="AO4" s="125" t="s">
         <v>46</v>
       </c>
-      <c r="AP4" s="121"/>
-      <c r="AQ4" s="121"/>
-      <c r="AR4" s="121"/>
-      <c r="AS4" s="111"/>
-      <c r="AT4" s="111"/>
-      <c r="AU4" s="112"/>
+      <c r="AP4" s="126"/>
+      <c r="AQ4" s="126"/>
+      <c r="AR4" s="126"/>
+      <c r="AS4" s="121"/>
+      <c r="AT4" s="121"/>
+      <c r="AU4" s="122"/>
     </row>
     <row r="5" spans="2:51" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -2860,10 +2965,10 @@
       <c r="AY12" s="34"/>
     </row>
     <row r="13" spans="2:51" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="118" t="s">
+      <c r="B13" s="136" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="117"/>
+      <c r="C13" s="135"/>
       <c r="H13" s="34"/>
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
@@ -2964,7 +3069,9 @@
         <v>17</v>
       </c>
       <c r="AF14" s="64"/>
-      <c r="AG14" s="59"/>
+      <c r="AG14" s="54">
+        <v>5</v>
+      </c>
       <c r="AH14" s="59"/>
       <c r="AI14" s="59"/>
       <c r="AK14" s="34"/>
@@ -3527,11 +3634,11 @@
       <c r="P23" s="71"/>
       <c r="Q23" s="71"/>
       <c r="R23" s="71"/>
-      <c r="T23" s="113" t="s">
+      <c r="T23" s="120" t="s">
         <v>35</v>
       </c>
-      <c r="U23" s="111"/>
-      <c r="V23" s="112"/>
+      <c r="U23" s="121"/>
+      <c r="V23" s="122"/>
       <c r="X23" s="59"/>
       <c r="Y23" s="59"/>
       <c r="Z23" s="59"/>
@@ -3555,17 +3662,17 @@
       <c r="AS23" s="71"/>
       <c r="AT23" s="71"/>
       <c r="AU23" s="71"/>
-      <c r="AW23" s="113" t="s">
+      <c r="AW23" s="120" t="s">
         <v>35</v>
       </c>
-      <c r="AX23" s="111"/>
-      <c r="AY23" s="112"/>
+      <c r="AX23" s="121"/>
+      <c r="AY23" s="122"/>
     </row>
     <row r="24" spans="2:51" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="119" t="s">
+      <c r="B24" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="117"/>
+      <c r="C24" s="135"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -3632,11 +3739,11 @@
       <c r="F25" s="47">
         <v>29</v>
       </c>
-      <c r="L25" s="123" t="s">
+      <c r="L25" s="127" t="s">
         <v>24</v>
       </c>
-      <c r="M25" s="124"/>
-      <c r="N25" s="112"/>
+      <c r="M25" s="128"/>
+      <c r="N25" s="122"/>
       <c r="S25" s="78" t="s">
         <v>43</v>
       </c>
@@ -3665,11 +3772,11 @@
       <c r="AG25" s="59"/>
       <c r="AH25" s="59"/>
       <c r="AI25" s="59"/>
-      <c r="AO25" s="123" t="s">
+      <c r="AO25" s="127" t="s">
         <v>24</v>
       </c>
-      <c r="AP25" s="124"/>
-      <c r="AQ25" s="112"/>
+      <c r="AP25" s="128"/>
+      <c r="AQ25" s="122"/>
       <c r="AV25" s="78" t="s">
         <v>43</v>
       </c>
@@ -3695,17 +3802,17 @@
       <c r="L26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="M26" s="125">
+      <c r="M26" s="129">
         <v>1</v>
       </c>
-      <c r="N26" s="126"/>
+      <c r="N26" s="130"/>
       <c r="P26" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="R26" s="122" t="s">
+      <c r="R26" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="S26" s="122"/>
+      <c r="S26" s="131"/>
       <c r="X26" s="51">
         <v>2</v>
       </c>
@@ -3727,17 +3834,17 @@
       <c r="AO26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AP26" s="125">
+      <c r="AP26" s="129">
         <v>1</v>
       </c>
-      <c r="AQ26" s="126"/>
+      <c r="AQ26" s="130"/>
       <c r="AS26" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AU26" s="122" t="s">
+      <c r="AU26" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="AV26" s="122"/>
+      <c r="AV26" s="131"/>
     </row>
     <row r="27" spans="2:51" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="23"/>
@@ -3753,21 +3860,21 @@
       <c r="L27" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="M27" s="127">
+      <c r="M27" s="118">
         <v>2</v>
       </c>
-      <c r="N27" s="128"/>
+      <c r="N27" s="119"/>
       <c r="P27" s="72" t="s">
         <v>4</v>
       </c>
       <c r="S27" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="T27" s="113" t="s">
+      <c r="T27" s="120" t="s">
         <v>36</v>
       </c>
-      <c r="U27" s="111"/>
-      <c r="V27" s="112"/>
+      <c r="U27" s="121"/>
+      <c r="V27" s="122"/>
       <c r="X27" s="51">
         <v>3</v>
       </c>
@@ -3789,21 +3896,21 @@
       <c r="AO27" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AP27" s="127">
+      <c r="AP27" s="118">
         <v>2</v>
       </c>
-      <c r="AQ27" s="128"/>
+      <c r="AQ27" s="119"/>
       <c r="AS27" s="72" t="s">
         <v>4</v>
       </c>
       <c r="AV27" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="AW27" s="113" t="s">
+      <c r="AW27" s="120" t="s">
         <v>36</v>
       </c>
-      <c r="AX27" s="111"/>
-      <c r="AY27" s="112"/>
+      <c r="AX27" s="121"/>
+      <c r="AY27" s="122"/>
     </row>
     <row r="28" spans="2:51" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="23"/>
@@ -3819,10 +3926,10 @@
       <c r="L28" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="M28" s="127">
+      <c r="M28" s="118">
         <v>3</v>
       </c>
-      <c r="N28" s="128"/>
+      <c r="N28" s="119"/>
       <c r="P28" s="5">
         <v>1</v>
       </c>
@@ -3857,10 +3964,10 @@
       <c r="AO28" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AP28" s="127">
+      <c r="AP28" s="118">
         <v>3</v>
       </c>
-      <c r="AQ28" s="128"/>
+      <c r="AQ28" s="119"/>
       <c r="AS28" s="5">
         <v>1</v>
       </c>
@@ -3888,10 +3995,10 @@
       <c r="L29" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="M29" s="127">
+      <c r="M29" s="118">
         <v>4</v>
       </c>
-      <c r="N29" s="128"/>
+      <c r="N29" s="119"/>
       <c r="P29">
         <v>0</v>
       </c>
@@ -3901,10 +4008,10 @@
       <c r="AO29" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="AP29" s="127">
+      <c r="AP29" s="118">
         <v>4</v>
       </c>
-      <c r="AQ29" s="128"/>
+      <c r="AQ29" s="119"/>
       <c r="AS29">
         <v>0</v>
       </c>
@@ -3916,10 +4023,10 @@
       <c r="L30" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="M30" s="114">
+      <c r="M30" s="123">
         <v>5</v>
       </c>
-      <c r="N30" s="115"/>
+      <c r="N30" s="124"/>
       <c r="P30">
         <v>15</v>
       </c>
@@ -3931,10 +4038,10 @@
       <c r="AO30" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="AP30" s="114">
+      <c r="AP30" s="123">
         <v>5</v>
       </c>
-      <c r="AQ30" s="115"/>
+      <c r="AQ30" s="124"/>
       <c r="AS30">
         <v>15</v>
       </c>
@@ -4964,16 +5071,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="AP27:AQ27"/>
-    <mergeCell ref="AW27:AY27"/>
-    <mergeCell ref="AP28:AQ28"/>
-    <mergeCell ref="AP29:AQ29"/>
-    <mergeCell ref="AP30:AQ30"/>
-    <mergeCell ref="AO4:AU4"/>
-    <mergeCell ref="AW23:AY23"/>
-    <mergeCell ref="AO25:AQ25"/>
-    <mergeCell ref="AP26:AQ26"/>
-    <mergeCell ref="AU26:AV26"/>
     <mergeCell ref="AB4:AE4"/>
     <mergeCell ref="T27:V27"/>
     <mergeCell ref="T23:V23"/>
@@ -4988,6 +5085,16 @@
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="M29:N29"/>
+    <mergeCell ref="AO4:AU4"/>
+    <mergeCell ref="AW23:AY23"/>
+    <mergeCell ref="AO25:AQ25"/>
+    <mergeCell ref="AP26:AQ26"/>
+    <mergeCell ref="AU26:AV26"/>
+    <mergeCell ref="AP27:AQ27"/>
+    <mergeCell ref="AW27:AY27"/>
+    <mergeCell ref="AP28:AQ28"/>
+    <mergeCell ref="AP29:AQ29"/>
+    <mergeCell ref="AP30:AQ30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
@@ -5024,38 +5131,38 @@
   </cols>
   <sheetData>
     <row r="9" spans="9:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I9" s="132"/>
-      <c r="M9" s="134"/>
+      <c r="I9" s="112"/>
+      <c r="M9" s="140"/>
     </row>
     <row r="10" spans="9:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I10" s="132"/>
-      <c r="M10" s="133"/>
-      <c r="R10" s="132"/>
-      <c r="S10" s="132"/>
+      <c r="I10" s="112"/>
+      <c r="M10" s="141"/>
+      <c r="R10" s="112"/>
+      <c r="S10" s="112"/>
     </row>
     <row r="11" spans="9:23" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="9:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I12" s="129"/>
-      <c r="M12" s="135" t="s">
+      <c r="I12" s="109"/>
+      <c r="M12" s="138" t="s">
         <v>4</v>
       </c>
-      <c r="R12" s="131" t="s">
+      <c r="R12" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="S12" s="131" t="s">
+      <c r="S12" s="111" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" spans="9:23" x14ac:dyDescent="0.25">
-      <c r="I13" s="129"/>
-      <c r="M13" s="136"/>
+      <c r="I13" s="109"/>
+      <c r="M13" s="139"/>
     </row>
     <row r="16" spans="9:23" x14ac:dyDescent="0.25">
-      <c r="U16" s="141" t="s">
+      <c r="U16" s="142" t="s">
         <v>51</v>
       </c>
-      <c r="V16" s="142"/>
-      <c r="W16" s="142"/>
+      <c r="V16" s="143"/>
+      <c r="W16" s="143"/>
     </row>
     <row r="20" spans="3:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="3:25" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5063,7 +5170,7 @@
     </row>
     <row r="22" spans="3:25" x14ac:dyDescent="0.25">
       <c r="K22" s="104"/>
-      <c r="Q22" s="129"/>
+      <c r="Q22" s="109"/>
     </row>
     <row r="23" spans="3:25" x14ac:dyDescent="0.25">
       <c r="K23" s="105"/>
@@ -5075,46 +5182,70 @@
       <c r="O24" s="103"/>
     </row>
     <row r="26" spans="3:25" x14ac:dyDescent="0.25">
-      <c r="Q26" s="140"/>
+      <c r="Q26" s="116"/>
     </row>
     <row r="29" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C29" s="108"/>
-      <c r="D29" s="130" t="s">
+      <c r="D29" s="110" t="s">
         <v>4</v>
       </c>
       <c r="E29" s="104"/>
       <c r="F29" s="105"/>
       <c r="G29" s="106"/>
-      <c r="U29" s="131"/>
+      <c r="U29" s="111"/>
       <c r="W29" s="108"/>
     </row>
     <row r="30" spans="3:25" x14ac:dyDescent="0.25">
       <c r="O30" s="107"/>
     </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C31" s="144" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="144"/>
+      <c r="E31" s="144"/>
+      <c r="F31" s="144"/>
+      <c r="G31" s="144"/>
+      <c r="T31" s="144" t="s">
+        <v>80</v>
+      </c>
+      <c r="U31" s="144"/>
+      <c r="V31" s="144"/>
+      <c r="W31" s="144"/>
+    </row>
     <row r="34" spans="11:23" x14ac:dyDescent="0.25">
       <c r="K34" s="108"/>
     </row>
+    <row r="41" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="L41" s="144" t="s">
+        <v>79</v>
+      </c>
+      <c r="M41" s="144"/>
+    </row>
     <row r="44" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="W44" s="140"/>
+      <c r="W44" s="116"/>
     </row>
     <row r="45" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="P45" s="132"/>
-      <c r="Q45" s="132"/>
-      <c r="T45" s="138"/>
-      <c r="W45" s="138"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="112"/>
+      <c r="T45" s="114"/>
+      <c r="W45" s="114"/>
     </row>
     <row r="47" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="P47" s="137" t="s">
+      <c r="P47" s="113" t="s">
         <v>4</v>
       </c>
-      <c r="Q47" s="137"/>
-      <c r="T47" s="139"/>
+      <c r="Q47" s="113"/>
+      <c r="T47" s="115"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="M9:M10"/>
     <mergeCell ref="U16:W16"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="T31:W31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5124,9 +5255,449 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="1.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="117"/>
+    <col min="8" max="8" width="21.28515625" customWidth="1"/>
+    <col min="9" max="9" width="4.85546875" customWidth="1"/>
+    <col min="10" max="10" width="2.28515625" customWidth="1"/>
+    <col min="11" max="11" width="16.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="117" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="117">
+        <v>38</v>
+      </c>
+      <c r="F2" s="117">
+        <f t="shared" ref="F2:F11" si="0">A2*E2</f>
+        <v>38</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="K2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+      <c r="N2">
+        <f>I2*M2</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="117">
+        <v>42</v>
+      </c>
+      <c r="F3" s="117">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="K3" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3">
+        <v>20</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ref="N3:N18" si="1">I3*M3</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="117">
+        <v>5</v>
+      </c>
+      <c r="F4" s="117">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="K4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" s="117">
+        <f>E4</f>
+        <v>5</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="117">
+        <v>5</v>
+      </c>
+      <c r="F5" s="117">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="K5" t="s">
+        <v>66</v>
+      </c>
+      <c r="M5" s="117">
+        <f>E11</f>
+        <v>3</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="117">
+        <v>6</v>
+      </c>
+      <c r="F6" s="117">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="K6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M6">
+        <v>20</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="117">
+        <v>45</v>
+      </c>
+      <c r="F7" s="117">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="K7" t="s">
+        <v>67</v>
+      </c>
+      <c r="M7">
+        <v>72</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="1"/>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="117">
+        <v>2</v>
+      </c>
+      <c r="F8" s="117">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="K8" t="s">
+        <v>68</v>
+      </c>
+      <c r="M8">
+        <v>50</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="117">
+        <v>35</v>
+      </c>
+      <c r="F9" s="117">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+      <c r="K9" t="s">
+        <v>69</v>
+      </c>
+      <c r="M9">
+        <v>20</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="117">
+        <v>5</v>
+      </c>
+      <c r="F10" s="117">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>4</v>
+      </c>
+      <c r="K10" t="s">
+        <v>70</v>
+      </c>
+      <c r="M10">
+        <v>5</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="117">
+        <v>3</v>
+      </c>
+      <c r="F11" s="117">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M11">
+        <v>35</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F12" s="117">
+        <f t="shared" ref="F12:F18" si="2">D12*E12</f>
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="K12" t="s">
+        <v>72</v>
+      </c>
+      <c r="M12">
+        <v>5</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F13" s="117">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="K13" t="s">
+        <v>73</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F14" s="117">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="K14" t="s">
+        <v>74</v>
+      </c>
+      <c r="M14">
+        <v>10</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F15" s="117">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="K15" t="s">
+        <v>77</v>
+      </c>
+      <c r="M15">
+        <v>5</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F16" s="117">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="K16" t="s">
+        <v>78</v>
+      </c>
+      <c r="M16">
+        <v>5</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="6:14" x14ac:dyDescent="0.25">
+      <c r="F17" s="117">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="6:14" x14ac:dyDescent="0.25">
+      <c r="F18" s="117">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="6:14" x14ac:dyDescent="0.25">
+      <c r="F20" s="117">
+        <f>SUM(F2:F18)</f>
+        <v>221</v>
+      </c>
+      <c r="N20" s="117">
+        <f>SUM(N2:N18)</f>
+        <v>537</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>